--- a/Configs/GameConfig/Datas/chapterInfo.xlsx
+++ b/Configs/GameConfig/Datas/chapterInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Git\TEngine_main\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC159092-7147-4560-B99E-B77536D548DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DD4C90-A3D4-46C1-BEF7-CA372C0D12D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="15" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>upgrade_item_list</t>
   </si>
   <si>
     <t>##type</t>
@@ -62,7 +59,7 @@
       <rPr>
         <sz val="16"/>
         <color theme="1"/>
-        <rFont val="黑体"/>
+        <rFont val="华文新魏"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
@@ -74,19 +71,31 @@
       <rPr>
         <sz val="16"/>
         <color theme="1"/>
-        <rFont val="黑体"/>
+        <rFont val="华文新魏"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>第二章：市场</t>
     </r>
   </si>
+  <si>
+    <t>item_list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,15 +113,22 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="黑体"/>
+      <name val="JetBrains Mono ExtraBold"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="华文新魏"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="JetBrains Mono ExtraBold"/>
+      <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -142,19 +158,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -480,61 +497,65 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="21.75" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="C4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" ht="21.75" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="21.75" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="5">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
